--- a/public/downloads/ecolabel-readiness-checklist.xlsx
+++ b/public/downloads/ecolabel-readiness-checklist.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>Ecolabel Readiness Checklist</t>
   </si>
@@ -84,6 +84,15 @@
     <t>Set each row to Ready / Partial / Not yet — the score updates automatically. Work the 'Not yet' next steps in order, weakest first.</t>
   </si>
   <si>
+    <t>Ready to act on this? Your next steps</t>
+  </si>
+  <si>
+    <t>1)  Build your free operational baseline  →  ecosystemsunited.com/tracker</t>
+  </si>
+  <si>
+    <t>2)  Answer the ESG &amp; Scope-3 questionnaires your buyers send, straight from your data  →  ESG Passport · €499 one-time, yours to own, no subscription</t>
+  </si>
+  <si>
     <t>Which Ecolabel Family Fits?</t>
   </si>
   <si>
@@ -186,10 +195,13 @@
     <t>Use it, then go further</t>
   </si>
   <si>
-    <t xml:space="preserve">  Pair this with the interactive selector at ecosystemsunited.com/tools/ecolabel-selector. When you're ready to apply, the 90-minute workshop maps your target label, its cost, and how to prepare: ecosystemsunited.com/workshops/ecolabel-certification.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Build the operational baseline that makes certification data easy to produce: ecosystemsunited.com/tracker (free).</t>
+    <t xml:space="preserve">  1) Pair this with the interactive selector at ecosystemsunited.com/tools/ecolabel-selector.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2) Build the free operational baseline that makes certification data easy to produce: ecosystemsunited.com/tracker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3) When buyers send ESG or Scope-3 questionnaires, answer them from your data with ESG Passport — €499 one-time, yours to own, no subscription.</t>
   </si>
   <si>
     <t>© Ecosystems United — Five Stacks Framework. Free to share.</t>
@@ -199,7 +211,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -234,6 +246,22 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF3D2E7C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <color rgb="FF1B6F55"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF3D2E7C"/>
     </font>
     <font>
@@ -245,7 +273,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,6 +305,11 @@
         <fgColor rgb="FF4AA88C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -290,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -326,13 +359,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -674,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -823,10 +865,37 @@
         <v>22</v>
       </c>
     </row>
+    <row r="14" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" showErrorMessage="1" error="Choose Ready, Partial, or Not yet" sqref="B10:B11">
@@ -836,6 +905,10 @@
       <formula1>"Ready,Partial,Not yet"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A15" r:id="rId1"/>
+    <hyperlink ref="A16" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -854,7 +927,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -862,7 +935,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -870,86 +943,86 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>29</v>
+      <c r="A5" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="C6" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>36</v>
+      <c r="A7" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>40</v>
+      <c r="A8" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>43</v>
+      <c r="A9" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -964,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -972,82 +1045,87 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>49</v>
+      <c r="A4" s="17" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>50</v>
+      <c r="A5" s="18" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>51</v>
+      <c r="A6" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>54</v>
+      <c r="A10" s="18" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="51" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>55</v>
+      <c r="A11" s="17" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>49</v>
+      <c r="A12" s="17" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" ht="51" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>57</v>
+      <c r="A13" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>49</v>
+      <c r="A15" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>59</v>
+      <c r="A17" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/ecolabel-readiness-checklist.xlsx
+++ b/public/downloads/ecolabel-readiness-checklist.xlsx
@@ -90,7 +90,7 @@
     <t>1)  Build your free operational baseline  →  ecosystemsunited.com/tracker</t>
   </si>
   <si>
-    <t>2)  Answer the ESG &amp; Scope-3 questionnaires your buyers send, straight from your data  →  ESG Passport · €499 one-time, yours to own, no subscription</t>
+    <t>2)  Answer the ESG &amp; Scope-3 questionnaires your buyers send, straight from your data  →  Ecosystems United Response Generator · from €39 per questionnaire</t>
   </si>
   <si>
     <t>Which Ecolabel Family Fits?</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">  2) Build the free operational baseline that makes certification data easy to produce: ecosystemsunited.com/tracker.</t>
   </si>
   <si>
-    <t xml:space="preserve">  3) When buyers send ESG or Scope-3 questionnaires, answer them from your data with ESG Passport — €499 one-time, yours to own, no subscription.</t>
+    <t xml:space="preserve">  3) When buyers send ESG or Scope-3 questionnaires, answer them from your data with the Ecosystems United Response Generator — from €39 per questionnaire.</t>
   </si>
   <si>
     <t>© Ecosystems United — Five Stacks Framework. Free to share.</t>
